--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B728CF1-FA0D-4044-AA9E-92B7C365DA5B}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E01EFCD0-0640-427A-B422-D7AE3384B01A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5395" uniqueCount="925">
   <si>
     <t>Category</t>
   </si>
@@ -2813,6 +2813,15 @@
   </si>
   <si>
     <t>Love and Sex Hexa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money Drawing Tall Hexa </t>
+  </si>
+  <si>
+    <t>Love and Sex Tall Hexa</t>
+  </si>
+  <si>
+    <t>Mama and Baby Tall Hexa</t>
   </si>
 </sst>
 </file>
@@ -8419,7 +8428,7 @@
         <v>24</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>386</v>
+        <v>922</v>
       </c>
       <c r="D277" s="18" t="s">
         <v>386</v>
@@ -8839,7 +8848,7 @@
         <v>24</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>381</v>
+        <v>923</v>
       </c>
       <c r="D307" s="17" t="s">
         <v>381</v>
@@ -8867,7 +8876,7 @@
         <v>24</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>383</v>
+        <v>924</v>
       </c>
       <c r="D309" s="17" t="s">
         <v>383</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A3C9D2-17B7-4710-BDCD-9B6671758F67}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6DC7F34-83E2-470C-A0A9-2EF5E4A8603B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3955,6 +3955,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10401,13 +10405,13 @@
         <v>48</v>
       </c>
       <c r="B411" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D411" s="14" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.45">
@@ -10415,13 +10419,13 @@
         <v>48</v>
       </c>
       <c r="B412" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D412" s="14" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.45">
@@ -10429,13 +10433,13 @@
         <v>48</v>
       </c>
       <c r="B413" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="D413" s="14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.45">
@@ -10443,13 +10447,13 @@
         <v>48</v>
       </c>
       <c r="B414" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="D414" s="14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.45">
@@ -10457,13 +10461,13 @@
         <v>48</v>
       </c>
       <c r="B415" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="D415" s="14" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.45">
@@ -10471,13 +10475,13 @@
         <v>48</v>
       </c>
       <c r="B416" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D416" s="14" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
@@ -10485,13 +10489,13 @@
         <v>48</v>
       </c>
       <c r="B417" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D417" s="14" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
@@ -10502,10 +10506,10 @@
         <v>24</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="D418" s="14" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.45">
@@ -10516,10 +10520,10 @@
         <v>24</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D419" s="14" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
@@ -10530,10 +10534,10 @@
         <v>24</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="D420" s="14" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
@@ -10544,10 +10548,10 @@
         <v>24</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D421" s="14" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.45">
@@ -10558,10 +10562,10 @@
         <v>24</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D422" s="14" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.45">
@@ -10572,10 +10576,10 @@
         <v>24</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="D423" s="14" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
@@ -10586,10 +10590,10 @@
         <v>24</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="D424" s="14" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
@@ -10600,10 +10604,10 @@
         <v>24</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D425" s="14" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.45">
@@ -10614,10 +10618,10 @@
         <v>24</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="D426" s="14" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
@@ -10628,10 +10632,10 @@
         <v>24</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D427" s="14" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.45">
@@ -10642,10 +10646,10 @@
         <v>24</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="D428" s="14" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.45">
@@ -10656,10 +10660,10 @@
         <v>24</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D429" s="14" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
@@ -10670,10 +10674,10 @@
         <v>24</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="D430" s="14" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.45">
@@ -10684,10 +10688,10 @@
         <v>24</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D431" s="14" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.45">
@@ -10698,10 +10702,10 @@
         <v>24</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D432" s="14" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.45">
@@ -10712,10 +10716,10 @@
         <v>24</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D433" s="14" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.45">
@@ -10726,10 +10730,10 @@
         <v>24</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="D434" s="14" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.45">
@@ -10740,10 +10744,10 @@
         <v>24</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="D435" s="14" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.45">
@@ -10754,10 +10758,10 @@
         <v>24</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D436" s="14" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.45">
@@ -10768,10 +10772,10 @@
         <v>24</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="D437" s="14" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.45">
@@ -10782,10 +10786,10 @@
         <v>24</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D438" s="14" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.45">
@@ -10795,11 +10799,15 @@
       <c r="B439" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C439" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="D439" s="14" t="s">
-        <v>554</v>
+      <c r="C439" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D439" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="F439" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.45">
@@ -10809,11 +10817,15 @@
       <c r="B440" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C440" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="D440" s="14" t="s">
-        <v>555</v>
+      <c r="C440" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D440" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="F440" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.45">
@@ -10823,11 +10835,15 @@
       <c r="B441" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C441" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="D441" s="14" t="s">
-        <v>556</v>
+      <c r="C441" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D441" s="17" t="s">
+        <v>915</v>
+      </c>
+      <c r="F441" s="14" t="e">
+        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.45">
@@ -10835,13 +10851,13 @@
         <v>48</v>
       </c>
       <c r="B442" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>557</v>
+        <v>526</v>
       </c>
       <c r="D442" s="14" t="s">
-        <v>557</v>
+        <v>526</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.45">
@@ -10849,13 +10865,13 @@
         <v>48</v>
       </c>
       <c r="B443" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>558</v>
+        <v>527</v>
       </c>
       <c r="D443" s="14" t="s">
-        <v>558</v>
+        <v>527</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.45">
@@ -10863,13 +10879,13 @@
         <v>48</v>
       </c>
       <c r="B444" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="D444" s="14" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.45">
@@ -10877,13 +10893,13 @@
         <v>48</v>
       </c>
       <c r="B445" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="D445" s="14" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.45">
@@ -10891,17 +10907,13 @@
         <v>48</v>
       </c>
       <c r="B446" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C446" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="D446" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="F446" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D446" s="14" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.45">
@@ -10909,17 +10921,13 @@
         <v>48</v>
       </c>
       <c r="B447" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C447" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D447" s="17" t="s">
-        <v>914</v>
-      </c>
-      <c r="F447" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D447" s="14" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.45">
@@ -10927,17 +10935,13 @@
         <v>48</v>
       </c>
       <c r="B448" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="D448" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="F448" s="14" t="e">
-        <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
-        <v>#REF!</v>
+        <v>23</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D448" s="14" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.45">

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/hem-catalogue-app_final-1/hem-catalogue-app-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hemcorporation-my.sharepoint.com/personal/analytics_hemcorporation_onmicrosoft_com/Documents/jitesh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="8_{B8F50426-6742-42C2-B694-AD00EF5BFA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{165920DF-25A0-419A-9A7A-B4804D75F872}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5B423D1-35D6-4C70-BBF2-4D40E6AE70F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B50F231-4B9C-4650-A2F8-A2334F1D3723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B04F0CB-8DFB-46E7-A522-5820D6CD8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2841,10 +2841,10 @@
     <t>Fresh Bergamote Car Freshner</t>
   </si>
   <si>
-    <t>Ocean Drive Car Freshner</t>
-  </si>
-  <si>
     <t>Peach Blossom Car Freshner</t>
+  </si>
+  <si>
+    <t>Aqua Car Freshner</t>
   </si>
 </sst>
 </file>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D61" s="16"/>
       <c r="E61" s="2"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>824</v>

--- a/Hem catalogue.xlsx
+++ b/Hem catalogue.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B04F0CB-8DFB-46E7-A522-5820D6CD8DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C40AC16-E664-43D3-B4E5-5635B7273333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5363" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5363" uniqueCount="932">
   <si>
     <t>Category</t>
   </si>
@@ -2764,9 +2764,6 @@
   </si>
   <si>
     <t>Hem Precious Chandan Soap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 CHAKRA </t>
   </si>
   <si>
     <t>Special Edition Square Gift Pack</t>
@@ -3160,7 +3157,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Hem Catalogue"/>
@@ -4365,13 +4361,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="22" t="s">
-        <v>906</v>
+        <v>612</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>612</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>818</v>
@@ -5082,7 +5078,7 @@
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="2"/>
@@ -5093,7 +5089,7 @@
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>822</v>
@@ -5106,7 +5102,7 @@
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>823</v>
@@ -5119,7 +5115,7 @@
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D60" s="16"/>
       <c r="E60" s="2"/>
@@ -5130,7 +5126,7 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D61" s="16"/>
       <c r="E61" s="2"/>
@@ -5141,7 +5137,7 @@
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>824</v>
@@ -6450,20 +6446,20 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E147" s="2"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="3" t="s">
@@ -6476,7 +6472,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B149" s="2"/>
       <c r="C149" s="3" t="s">
@@ -6489,14 +6485,14 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B150" s="2"/>
       <c r="C150" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F150" s="14" t="e">
         <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
@@ -6505,7 +6501,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="3" t="s">
@@ -6520,7 +6516,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="3" t="s">
@@ -6616,7 +6612,7 @@
         <v>24</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D158" s="16" t="s">
         <v>840</v>
@@ -6631,7 +6627,7 @@
         <v>24</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D159" s="16" t="s">
         <v>841</v>
@@ -6676,7 +6672,7 @@
         <v>24</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D162" s="16" t="s">
         <v>126</v>
@@ -8714,7 +8710,7 @@
         <v>24</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D298" s="17" t="s">
         <v>227</v>
@@ -12104,7 +12100,7 @@
       </c>
       <c r="B522" s="2"/>
       <c r="C522" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D522" s="11" t="s">
         <v>898</v>
@@ -12267,7 +12263,7 @@
       </c>
       <c r="B533" s="2"/>
       <c r="C533" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D533" s="11" t="s">
         <v>788</v>
@@ -12282,7 +12278,7 @@
       </c>
       <c r="B534" s="2"/>
       <c r="C534" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D534" s="11" t="s">
         <v>890</v>
@@ -12297,7 +12293,7 @@
       </c>
       <c r="B535" s="2"/>
       <c r="C535" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D535" s="11" t="s">
         <v>790</v>
@@ -12327,7 +12323,7 @@
       </c>
       <c r="B537" s="2"/>
       <c r="C537" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D537" s="11" t="s">
         <v>892</v>
@@ -12342,7 +12338,7 @@
       </c>
       <c r="B538" s="2"/>
       <c r="C538" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D538" s="11" t="s">
         <v>789</v>
@@ -12563,7 +12559,7 @@
         <v>61</v>
       </c>
       <c r="D551" s="19" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E551" s="19"/>
       <c r="F551" s="14"/>
@@ -13183,7 +13179,7 @@
         <v>24</v>
       </c>
       <c r="C591" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D591" s="19" t="s">
         <v>514</v>
@@ -13752,7 +13748,7 @@
         <v>807</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F631" s="14" t="e">
         <f>_xlfn.XLOOKUP(#REF!,'[1]Hem Catalogue'!$C$545:$C$643,'[1]Hem Catalogue'!$D$545:$D$643,"")</f>
@@ -14075,7 +14071,7 @@
         <v>24</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>386</v>
@@ -14502,7 +14498,7 @@
         <v>24</v>
       </c>
       <c r="C683" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D683" s="2" t="s">
         <v>381</v>
@@ -14530,7 +14526,7 @@
         <v>24</v>
       </c>
       <c r="C685" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D685" s="2" t="s">
         <v>383</v>
